--- a/artfynd/A 31170-2021 artfynd.xlsx
+++ b/artfynd/A 31170-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31170-2021 artfynd.xlsx
+++ b/artfynd/A 31170-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97336032</v>
+        <v>97336006</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582376.9961542445</v>
+        <v>582082</v>
       </c>
       <c r="R2" t="n">
-        <v>6320001.11223897</v>
+        <v>6320162</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97336040</v>
+        <v>97336021</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -856,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granshult 1:2, Sm</t>
+          <t>Granshult 1:7, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582392.386574303</v>
+        <v>582168</v>
       </c>
       <c r="R3" t="n">
-        <v>6319995.428105966</v>
+        <v>6320161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,6 +920,254 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97336032</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granshult 1:7, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>582377</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6320001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97336040</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granshult 1:2, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>582392</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6319995</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
